--- a/template.xlsx
+++ b/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ricardo/repos/bracket-creator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3D0668-294F-6947-8681-E89465840FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A60E6A-A4D4-BD4D-B8C2-6D02E90C81E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34720" yWindow="1400" windowWidth="38080" windowHeight="20800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -45,10 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
-  <si>
-    <t>Elimination Round 1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Tournament Pools</t>
   </si>
@@ -183,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -206,48 +203,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -285,15 +245,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1644,28 +1596,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="51" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
@@ -1756,26 +1708,26 @@
     </row>
     <row r="7" spans="1:8" ht="51" x14ac:dyDescent="0.15">
       <c r="A7" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
@@ -1862,7 +1814,7 @@
     <row r="2" spans="1:8" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -1948,29 +1900,24 @@
     <col min="16" max="16384" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="19"/>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
